--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulocardoso\workspace\projetos\inventory_app__oracle_wms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871181F4-1698-44B3-9976-C24B414A93DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEB67D1-D9C7-4E20-8CFD-004A0DF15BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9AF81059-ECB7-402F-9516-593B96A0ACFE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>COLABORADOR</t>
   </si>
@@ -50,18 +50,12 @@
     <t>USUARIO</t>
   </si>
   <si>
-    <t>CARGOS</t>
-  </si>
-  <si>
     <t>AMANDA SILVA SOUZA</t>
   </si>
   <si>
     <t>asouza</t>
   </si>
   <si>
-    <t>AUXILIAR DE LOGISTICA I - ARCO</t>
-  </si>
-  <si>
     <t>ELAINE APARECIDA BELEM</t>
   </si>
   <si>
@@ -74,9 +68,6 @@
     <t>emmarcelino</t>
   </si>
   <si>
-    <t>AUXILIAR DE LOGISTICA  II - ARCO</t>
-  </si>
-  <si>
     <t>FRANCIELE CRISTINA ALVES FONSECA</t>
   </si>
   <si>
@@ -110,12 +101,6 @@
     <t>jmarques</t>
   </si>
   <si>
-    <t>MARIA ALINE CAVALCANTE MACIEL</t>
-  </si>
-  <si>
-    <t>mamaciel</t>
-  </si>
-  <si>
     <t>MARIA LENILZA GOMES DA SILVA</t>
   </si>
   <si>
@@ -128,12 +113,6 @@
     <t>maferreira</t>
   </si>
   <si>
-    <t>MARIANA SANTOS PEREIRA</t>
-  </si>
-  <si>
-    <t>mspereira</t>
-  </si>
-  <si>
     <t>NATALY PAIXÃO SILVA</t>
   </si>
   <si>
@@ -191,9 +170,6 @@
     <t>bebatista</t>
   </si>
   <si>
-    <t>ASSISTENTE DE OPERAÇÕES</t>
-  </si>
-  <si>
     <t>IRENE FERREIRA DE LIMA</t>
   </si>
   <si>
@@ -227,13 +203,37 @@
     <t>JAQUELINE FERNANDES</t>
   </si>
   <si>
-    <t xml:space="preserve">LEANDRO </t>
-  </si>
-  <si>
-    <t>lrsilva</t>
-  </si>
-  <si>
-    <t>BRUNA EMANUELE GONÇALVES BATISTA</t>
+    <t>ERICA DE SOUSA CONCEICAO</t>
+  </si>
+  <si>
+    <t>esconceicao</t>
+  </si>
+  <si>
+    <t>FABRICIA CORDEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>fcsilva</t>
+  </si>
+  <si>
+    <t>JOSIANE APARECIDA DA SILVA BASILIO</t>
+  </si>
+  <si>
+    <t>jabasilio</t>
+  </si>
+  <si>
+    <t>NATHALIA FERREIRA DINIZ</t>
+  </si>
+  <si>
+    <t>nfdiniz</t>
+  </si>
+  <si>
+    <t>QIZY SANDE SOUZA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>qsoliveira</t>
+  </si>
+  <si>
+    <t>BRUNA EMANUELE GONCALVES BATISTA</t>
   </si>
 </sst>
 </file>
@@ -612,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D1C801-28C5-463D-99D3-B56E9081588F}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.36328125" bestFit="1" customWidth="1"/>
@@ -621,424 +621,261 @@
     <col min="4" max="4" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="B19" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="B23" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="B26" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B28" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B29" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B30" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B32" t="s">
         <v>51</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulocardoso\workspace\projetos\inventory_app__oracle_wms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEB67D1-D9C7-4E20-8CFD-004A0DF15BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5034A6-048F-464F-82DB-0C3A958EEED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9AF81059-ECB7-402F-9516-593B96A0ACFE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>COLABORADOR</t>
   </si>
@@ -234,6 +234,36 @@
   </si>
   <si>
     <t>BRUNA EMANUELE GONCALVES BATISTA</t>
+  </si>
+  <si>
+    <t>LEVI</t>
+  </si>
+  <si>
+    <t>lnsantos</t>
+  </si>
+  <si>
+    <t>EDY</t>
+  </si>
+  <si>
+    <t>ezane</t>
+  </si>
+  <si>
+    <t>GABRIELA SELLAN RIBEIRO</t>
+  </si>
+  <si>
+    <t>gribeiro</t>
+  </si>
+  <si>
+    <t>MARIA ALINE CAVALCANTE MACIEL</t>
+  </si>
+  <si>
+    <t>mamaciel</t>
+  </si>
+  <si>
+    <t>MARIANA SANTOS PEREIRA</t>
+  </si>
+  <si>
+    <t>mspereira</t>
   </si>
 </sst>
 </file>
@@ -612,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D1C801-28C5-463D-99D3-B56E9081588F}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.36328125" bestFit="1" customWidth="1"/>
@@ -878,6 +908,46 @@
         <v>51</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
